--- a/LubanConfig/Moba/Production/Datas/J-效果表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-效果表.xlsx
@@ -1106,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U40"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="3"/>
@@ -1585,7 +1585,7 @@
       <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
       <c r="O6" s="5" t="n">
-        <v>0</v>
+        <v>90001002</v>
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       <c r="M32" s="5" t="n"/>
       <c r="N32" s="5" t="n"/>
       <c r="O32" s="5" t="n">
-        <v>90003001</v>
+        <v>90007005</v>
       </c>
       <c r="P32" s="5" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>100025</t>
+          <t>100026</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -3304,7 +3304,7 @@
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
       <c r="O36" s="5" t="n">
-        <v>90006003</v>
+        <v>90007006</v>
       </c>
       <c r="P36" s="5" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>0</v>
@@ -3408,12 +3408,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>100014</t>
+          <t>100010</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>鲁班七号-河豚手雷眩晕</t>
+          <t>鲁班七号-河豚手雷减速</t>
         </is>
       </c>
       <c r="L38" s="5" t="n"/>
@@ -3530,7 +3530,7 @@
       <c r="M40" s="5" t="n"/>
       <c r="N40" s="5" t="n"/>
       <c r="O40" s="5" t="n">
-        <v>90006003</v>
+        <v>90008005</v>
       </c>
       <c r="P40" s="5" t="inlineStr">
         <is>
@@ -3547,6 +3547,64 @@
       <c r="U40" s="5" t="inlineStr">
         <is>
           <t>DispelBlockedByTagNames,TagNames</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="n">
+        <v>10070202</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>LegacyTag</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>100027</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>孙尚香-红莲爆弹-破甲</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n">
+        <v>90007006</v>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>KeepRemaining</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S41" s="5" t="n"/>
+      <c r="T41" s="5" t="n"/>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>DispelBlockedByTagNames</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -6278,6 +6336,34 @@
       </c>
       <c r="F38" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>100026</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1000026</v>
+      </c>
+      <c r="F39" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>100027</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1000027</v>
+      </c>
+      <c r="F40" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -6291,7 +6377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="27.125" customWidth="1" min="3" max="3"/>
@@ -8579,6 +8665,86 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1000026</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SunShangxiangArmorBreak</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1|8</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3|-0.15</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3|0|0|1.5|0|0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0|0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1000027</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SunShangxiangSkill2ArmorBreak</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1|8</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3|-0.15</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3|0|0|1.5|0|0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0|0</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LubanConfig/Moba/Production/Datas/J-效果表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-效果表.xlsx
@@ -1701,7 +1701,7 @@
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
       <c r="O37" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P37" s="5" t="inlineStr">
         <is>
